--- a/data/daily/2026-10/2026-10-27.xlsx
+++ b/data/daily/2026-10/2026-10-27.xlsx
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 로네펠트 기프트 에디션 (티백 5종증정)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>35,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1565,29 +1565,33 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026112036_e3a7e53364444920a21456d555f6b17c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261027092029_af14b962a57c4de9940654af7e1928f7.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16354</v>
+        <v>16355</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 상자 패키지가 깔끔하고 고급스러우며 증정 구성도 알참</t>
+          <t>고급스러운 패키지 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 섭취 후 피로가 잘 풀리고 확실한 활력을 제공함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>피로 회복 및 활력 증진 — 복용 후 피로 회복 및 활력 증진 효과를 느낌</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>알찬 상품 구성 — 티백 증정 등 전용 특별 구성이 알차고 만족스러움</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>아쉬운 쇼핑백 구성 옵션 — 선물 전달 시 필요한 쇼핑백이 기본 구성에 없어 아쉬움</t>
+          <t>쇼핑백 부재의 아쉬움 — 직접 전달 시 필요한 쇼핑백이 포함되지 않아 난감함</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -1635,12 +1639,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>세련되고 고급스러운 포장 — 패키지가 세련되어 선물받았을 때 만족도가 높음</t>
+          <t>세련되고 고급진 포장 — 패키지가 세련되고 포장이 고급스러워 선물용으로 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>간편한 액상 알약 복용 — 알약과 액상이 함께 들어 있어 부담 없이 간편하게 섭취 가능함</t>
+          <t>간편한 복용 방법 — 액상과 알약이 함께 구성되어 있어 부담 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -1690,15 +1694,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 체력 및 피로 개선 — 체력이 달릴 때 섭취 시 에너지 상승 및 피로 회복 효과가 있음</t>
+          <t>확실한 체력 증진 효과 — 복용 시 속이 편안하고 확실하게 에너지와 기운이 나는 효과가 있음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>진하고 깊은 액상 농도 — 다른 액상 제품에 비해 액상 비타민 농도가 확실히 짙음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>진하고 깊은 액상 농도 — 타사 액상 제품에 비해 농도가 찐하여 만족스러움</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>선물용 만족도 우수 — 제품 인지도가 높고 구성이 좋아 선물용으로 기분 좋음</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -1741,27 +1749,27 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>6537</v>
+        <v>6538</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>젤리 형태의 맛있는 식감 — 적당한 말랑함과 은은한 단맛으로 기분 좋게 섭취함</t>
+          <t>맛있고 편리한 젤리 제형 — 물 없이 간식처럼 맛있고 간편하게 씹어 먹을 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>간편한 비타민 섭취 방식 — 젤리 제형이라 번거로움 없이 매일 챙겨 먹기 편함</t>
+          <t>적당한 단맛과 쫄깃함 — 과하게 달지 않고 쫄깃하여 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>개봉 시 인내심 요구 — 포장이 잘 개봉되지 않아서 뜯을 때 불편함</t>
+          <t>개봉 포장의 불편함 — 포장 비닐이 잘 뜯겨지지 않아 개봉 시 인내심이 필요함</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>어른 영양제 느낌 부족 — 하리보 같은 식감으로 어린이 비타민 같은 느낌이 강함</t>
+          <t>유아용 비타민 느낌 — 어른용 영양제보다는 하리보 젤리나 유아용 비타민 느낌이 강함</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -1808,12 +1816,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>피로 해소와 활력 부여 — 환절기나 피로한 일상에 피로 회복과 상쾌함을 줌</t>
+          <t>피로 회복 및 체력 유지 — 피로 회복에 아주 좋고 환절기 체력 버티기에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>편안한 섭취 및 휴대성 — 휴대하기 편하고 먹기도 편해서 지속적인 복용이 용이함</t>
+          <t>편리한 섭취와 휴대성 — 먹기 편하고 휴대하기 좋아 간편하게 비타민을 챙기기 좋음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -1863,17 +1871,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 패키지 구성이 깔끔하고 고급스러워 선물용으로 적합함</t>
+          <t>고급스러운 패키지와 증정 — 깔끔하고 고급스러운 포장에 1입 추가 증정 혜택이 포함됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>재미있는 섞어 먹는 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 먹는 과정이 신선함</t>
+          <t>이색적이고 간편한 복용 — 버튼을 눌러 분말과 액상을 섞어 먹는 방식이 이색적이고 편함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>부담 없는 자극 적은 맛 — 신맛이 적고 상큼한 단맛이 어우러져 목넘김이 좋음</t>
+          <t>거부감 없는 상큼한 맛 — 신맛이 적고 상큼하며 달콤하여 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1918,16 +1926,16 @@
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>8766</v>
+        <v>8767</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>간편한 마시는 액상 타입 — 액상 형태로 간편하게 섭취할 수 있어 바쁜 아침에 용이함</t>
+          <t>간편한 섭취와 피로 개선 — 아침이나 피곤할 때 간편하게 먹고 활력을 얻기에 적합함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>빠른 피로 회복 성능 — 아침 피로감을 줄여주고 기운을 차리는 데 도움을 줌</t>
+          <t>신속한 배송 서비스 — 배송이 빠르고 안전하게 도착함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -1977,18 +1985,18 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1포 구성의 뛰어난 편의성 — 한 포로 영양소를 간편하게 챙길 수 있어 복용이 편함</t>
+          <t>개별 포장의 편의성 — 한 포씩 포장되어 있어 들고 다니며 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>꾸준한 체력 개선 효과 — 지속적으로 복용 시 활력이 생기고 피로가 개선되는 것을 느낌</t>
+          <t>체력 증진과 활력 개선 — 꾸준히 섭취하면 몸에 힘이 나는 것을 체감함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 구성 — 동봉된 사은품의 품질이 저렴한 제품 같아 아쉬움</t>
+          <t>아쉬운 사은품 품질 — 사은품 구성이 시중 다이소 판매 제품으로 제공되어 아쉬움</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -2036,18 +2044,18 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>바쁜 일상 속 확실한 활력 — 바쁘고 피곤한 상황에서 활력을 높여주는 효과가 뛰어남</t>
+          <t>확실한 활력 충전 효과 — 바쁘고 힘들 때 섭취하면 활력이 돋고 효과가 확실함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>편안한 속과 섭취감 — 복용이 편하고 속 부담 없이 잘 맞음</t>
+          <t>양호한 배송 및 섭취 편의 — 배송 상태가 양호하며 섭취하기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>호불호 갈리는 감기약 맛 — 오렌지약 또는 감기약 맛이 느껴져 맛에 대한 아쉬움이 있음</t>
+          <t>아쉬운 감기약 느낌 맛 — 오렌지 맛이 감기약 느낌과 유사하여 맛 면에서 아쉬움</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -2095,18 +2103,18 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>빠른 배송과 높은 신뢰도 — 주문 후 배송 처리가 매우 빠르게 이뤄짐</t>
+          <t>고함량 비타민C 선사 — 3000mg의 높은 용량으로 피로 회복과 리프레쉬에 도움 됨</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>고함량 3000mg 함유량 — 높은 비타민C 용량으로 활력 및 리프레쉬에 효과적임</t>
+          <t>신속한 배송 서비스 — 주문 후 배송이 매우 빠르게 도착함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>매우 강한 신맛의 자극 — 분말 그대로 섭취 시 신맛이 지나치게 강해 물과 함께 복용해야 함</t>
+          <t>매우 강한 신맛 — 분말 제형 특성상 신맛이 강해 물 없이 섭취하기 어려움</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -2150,21 +2158,21 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>더부룩함 줄이는 소화 개선 — 속 답답함과 소화 불량을 빠르게 가라앉혀 편안함을 줌</t>
+          <t>더부룩함 및 소화 개선 — 섭취 후 더부룩함이 개선되고 속이 편안해짐을 느낌</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>풍성하고 저렴한 사은품 — 추가 포수 및 단백질바 등 증정 구성품이 풍성하고 가성비가 높음</t>
+          <t>풍성한 증정품 구성 — 추가 10포와 단백질바 등 다양한 사은품 구성이 풍성함</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>고소하고 부담 없는 풍미 — 고소한 맛이 나서 질리지 않고 지속적으로 먹기 좋음</t>
+          <t>고소하고 맛있는 맛 — 고소하고 맛있어 거부감 없이 매일 먹기 좋음</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2213,17 +2221,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>개별 스틱 타입의 편리성 — 가방에 넣고 다니기 쉽고 복용 타이밍을 맞추기 용이함</t>
+          <t>뛰어난 숙취 해소 효과 — 음주 전후 섭취 시 다음날 속이 편안하고 회복이 빠름</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>우수한 숙취 해소 성능 — 음주 전후 섭취 시 다음 날 숙취 없이 속이 편안함</t>
+          <t>깔끔한 패키지 구성 — 세트 포장이 세련되고 구성이 넉넉하여 지인 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>깔끔하고 가벼운 목넘김 — 텁텁함이 없고 깔끔한 고농축 제형이라 부담 없이 넘어감</t>
+          <t>간편한 휴대와 목넘김 — 스틱 개별 포장이라 휴대하기 쉽고 맛이 텁텁하지 않음</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2272,12 +2280,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 살이 촉촉하여 식감이 뛰어남</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 부드러워 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>다양하고 질리지 않는 맛 — 종류가 다채로워 질리지 않고 지속적으로 다이어트 식단을 이어감</t>
+          <t>질리지 않는 다양한 맛 — 36가지의 다채로운 맛으로 구성되어 매일 먹어도 질리지 않음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -2327,16 +2335,24 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>속이 편안한 소화 지원 — 과식이나 밀가루 음식 섭취 후 답답한 속을 신속하게 완화함</t>
+          <t>속 더부룩함 및 소화 개선 — 밀가루나 외식 후 섭취 시 소화가 잘되고 속이 편안해짐</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>미숫가루 같은 고소함 — 텁텁하지 않고 꼬수운 미숫가루 맛이 나서 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소한 맛이 나 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>알찬 상품과 증정 구성 — 추가 증정포와 견과류바 등 구성이 풍성하여 만족스러움</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>증정 기프티콘 안내 미흡 — 이벤트 기프티콘 수령 및 확인 방법에 대한 안내가 부족함</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
@@ -2378,16 +2394,16 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>취향 저격의 맛있는 효소 — 크림소다, 쿠키앤크림 등 기분 좋게 먹을 수 있는 풍미임</t>
+          <t>다양하고 맛있는 맛 — 쿠키앤크림, 크림소다 등 다양한 맛이 모두 맛있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>푸짐하고 센스 있는 사은품 — 포토카드 및 단백질바 등 추가 구성품이 알차게 동봉됨</t>
+          <t>매력적인 포토카드 증정 — 아이돌 포토카드와 단백질바 구성이 포함되어 만족스러움</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -2437,15 +2453,19 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>전자레인지 조리의 간편함 — 데우기만 하면 바로 먹을 수 있어 식사 대용으로 편함</t>
+          <t>촉촉한 식감과 다채로운 맛 — 특색 있고 맛있는 양념과 촉촉한 식감이 만족스러움</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>다채롭고 촉촉한 식감 — 떡볶이 맛 등 맛이 다양하고 부드러워 식단 관리에 유용함</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>간편한 전자레인지 조리 — 전자레인지에 데우기만 하면 되어 간편하게 먹기 편함</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>저렴한 가격과 빠른 배송 — 다양한 구성 대비 가격이 저렴하고 배송이 빠름</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -2453,7 +2473,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2461,58 +2481,54 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>가농</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>39,000원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14380726</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261026100840_629c26bcd34b4b2c9b2b3dbda7297fd4.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>35</v>
+        <v>761</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>계란 흰자의 간편한 영양 — 노른자 없이 비리지 않은 흰자만으로 부담 없이 단백질을 챙김</t>
+          <t>고급스럽고 예쁜 포장 — 패키지와 오간자 포장이 예뻐 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>자극 없이 다양한 풍미 — 훈제, 짭짤한 맛 등 종류가 다양해 간식으로 즐기기 좋음</t>
+          <t>거부감 없는 맛과 편리함 — 앰플 제형으로 맛이 좋고 하루 한 병 간편하게 섭취함</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>다소 깨끗하지 않은 박스 — 배송된 포장 박스 상태가 깨끗하지 않아 아쉬움</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="B19" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2520,48 +2536,56 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>가농</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>39,000원</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/14380726</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261026100840_629c26bcd34b4b2c9b2b3dbda7297fd4.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261021165641_99634da9bf9f4b3d8e560929369229b1.png</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>761</v>
+        <v>35</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 패키지 — 오간자 포장과 플리츠백 등 디자인이 인상적임</t>
+          <t>깔끔한 흰자 단백질 — 노른자가 없어 퍽퍽하지 않고 비리지 않게 단백질을 챙김</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>기분 좋은 맛과 섭취 편의 — 맛이 좋고 하루 한 병씩 마시기 간편함</t>
+          <t>껍질 까기 없는 간편함 — 껍질을 까는 번거로움 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>단일 맛 구성의 아쉬움 — 여러 맛을 섞어 구매할 수 있는 혼합 옵션이 없어 아쉬움</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>박스 포장 상태 미흡 — 외포장 박스가 재활용된 듯 깨끗하지 않은 상태로 도착함</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -2602,16 +2626,16 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>다채로운 20종 패키지 — 종류가 많아 매일 질리지 않고 다이어트 식단을 즐길 수 있음</t>
+          <t>질리지 않는 다채로운 메뉴 — 닭가슴살 외 다양한 종류가 포함되어 질리지 않고 먹기 좋음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>촉촉한 식감과 조리 편의 — 부드러운 육질에 전자레인지 전용 용기가 포함되어 조리가 편리함</t>
+          <t>렌지용 용기 제공의 편리함 — 증정받은 전용 용기 덕분에 전자레인지 조리가 편리함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2661,12 +2685,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤함 — 느끼하거나 비리지 않고 일반 음료처럼 달콤하게 마실 수 있음</t>
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이나 느끼함 없이 달콤하게 마심</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>포만감 있는 운동 후 보충 — 운동 후 단백질 보충에 용이하며 적절한 포만감을 유지해줌</t>
+          <t>든든한 포만감 형성 — 운동 후나 간식 대용으로 마시면 은근히 포만감이 생김</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -2899,7 +2923,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 단독 기프트박스 증정 (공식수입)</t>
+          <t>독일 명품 비타민 오쏘몰 이뮨 멀티비타민&amp;미네랄 7입 - 로네펠트 기프트 에디션 (티백 5종증정)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -2992,7 +3016,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16354</v>
+        <v>16355</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>15694</v>
@@ -3001,7 +3025,7 @@
         <v>3425</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6537</v>
+        <v>6538</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>834</v>
@@ -3010,7 +3034,7 @@
         <v>1810</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>8766</v>
+        <v>8767</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>99</v>
@@ -3030,63 +3054,65 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 상자 패키지가 깔끔하고 고급스러우며 증정 구성도 알참
-우수한 피로 회복 효과 — 섭취 후 피로가 잘 풀리고 확실한 활력을 제공함</t>
+          <t>고급스러운 패키지 — 상자 패키지가 깔끔하고 고급스러워 선물용으로 적합함
+피로 회복 및 활력 증진 — 복용 후 피로 회복 및 활력 증진 효과를 느낌
+알찬 상품 구성 — 티백 증정 등 전용 특별 구성이 알차고 만족스러움</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>세련되고 고급스러운 포장 — 패키지가 세련되어 선물받았을 때 만족도가 높음
-간편한 액상 알약 복용 — 알약과 액상이 함께 들어 있어 부담 없이 간편하게 섭취 가능함</t>
+          <t>세련되고 고급진 포장 — 패키지가 세련되고 포장이 고급스러워 선물용으로 좋음
+간편한 복용 방법 — 액상과 알약이 함께 구성되어 있어 부담 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 체력 및 피로 개선 — 체력이 달릴 때 섭취 시 에너지 상승 및 피로 회복 효과가 있음
-진하고 깊은 액상 농도 — 다른 액상 제품에 비해 액상 비타민 농도가 확실히 짙음</t>
+          <t>확실한 체력 증진 효과 — 복용 시 속이 편안하고 확실하게 에너지와 기운이 나는 효과가 있음
+진하고 깊은 액상 농도 — 타사 액상 제품에 비해 농도가 찐하여 만족스러움
+선물용 만족도 우수 — 제품 인지도가 높고 구성이 좋아 선물용으로 기분 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>젤리 형태의 맛있는 식감 — 적당한 말랑함과 은은한 단맛으로 기분 좋게 섭취함
-간편한 비타민 섭취 방식 — 젤리 제형이라 번거로움 없이 매일 챙겨 먹기 편함</t>
+          <t>맛있고 편리한 젤리 제형 — 물 없이 간식처럼 맛있고 간편하게 씹어 먹을 수 있음
+적당한 단맛과 쫄깃함 — 과하게 달지 않고 쫄깃하여 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소와 활력 부여 — 환절기나 피로한 일상에 피로 회복과 상쾌함을 줌
-편안한 섭취 및 휴대성 — 휴대하기 편하고 먹기도 편해서 지속적인 복용이 용이함</t>
+          <t>피로 회복 및 체력 유지 — 피로 회복에 아주 좋고 환절기 체력 버티기에 도움 됨
+편리한 섭취와 휴대성 — 먹기 편하고 휴대하기 좋아 간편하게 비타민을 챙기기 좋음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물 포장 — 패키지 구성이 깔끔하고 고급스러워 선물용으로 적합함
-재미있는 섞어 먹는 방식 — 버튼을 눌러 분말과 액상을 직접 섞어 먹는 과정이 신선함
-부담 없는 자극 적은 맛 — 신맛이 적고 상큼한 단맛이 어우러져 목넘김이 좋음</t>
+          <t>고급스러운 패키지와 증정 — 깔끔하고 고급스러운 포장에 1입 추가 증정 혜택이 포함됨
+이색적이고 간편한 복용 — 버튼을 눌러 분말과 액상을 섞어 먹는 방식이 이색적이고 편함
+거부감 없는 상큼한 맛 — 신맛이 적고 상큼하며 달콤하여 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>간편한 마시는 액상 타입 — 액상 형태로 간편하게 섭취할 수 있어 바쁜 아침에 용이함
-빠른 피로 회복 성능 — 아침 피로감을 줄여주고 기운을 차리는 데 도움을 줌</t>
+          <t>간편한 섭취와 피로 개선 — 아침이나 피곤할 때 간편하게 먹고 활력을 얻기에 적합함
+신속한 배송 서비스 — 배송이 빠르고 안전하게 도착함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1포 구성의 뛰어난 편의성 — 한 포로 영양소를 간편하게 챙길 수 있어 복용이 편함
-꾸준한 체력 개선 효과 — 지속적으로 복용 시 활력이 생기고 피로가 개선되는 것을 느낌</t>
+          <t>개별 포장의 편의성 — 한 포씩 포장되어 있어 들고 다니며 챙겨 먹기 편함
+체력 증진과 활력 개선 — 꾸준히 섭취하면 몸에 힘이 나는 것을 체감함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>바쁜 일상 속 확실한 활력 — 바쁘고 피곤한 상황에서 활력을 높여주는 효과가 뛰어남
-편안한 속과 섭취감 — 복용이 편하고 속 부담 없이 잘 맞음</t>
+          <t>확실한 활력 충전 효과 — 바쁘고 힘들 때 섭취하면 활력이 돋고 효과가 확실함
+양호한 배송 및 섭취 편의 — 배송 상태가 양호하며 섭취하기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>빠른 배송과 높은 신뢰도 — 주문 후 배송 처리가 매우 빠르게 이뤄짐
-고함량 3000mg 함유량 — 높은 비타민C 용량으로 활력 및 리프레쉬에 효과적임</t>
+          <t>고함량 비타민C 선사 — 3000mg의 높은 용량으로 피로 회복과 리프레쉬에 도움 됨
+신속한 배송 서비스 — 주문 후 배송이 매우 빠르게 도착함</t>
         </is>
       </c>
     </row>
@@ -3098,15 +3124,15 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 쇼핑백 구성 옵션 — 선물 전달 시 필요한 쇼핑백이 기본 구성에 없어 아쉬움</t>
+          <t>쇼핑백 부재의 아쉬움 — 직접 전달 시 필요한 쇼핑백이 포함되지 않아 난감함</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>개봉 시 인내심 요구 — 포장이 잘 개봉되지 않아서 뜯을 때 불편함
-어른 영양제 느낌 부족 — 하리보 같은 식감으로 어린이 비타민 같은 느낌이 강함</t>
+          <t>개봉 포장의 불편함 — 포장 비닐이 잘 뜯겨지지 않아 개봉 시 인내심이 필요함
+유아용 비타민 느낌 — 어른용 영양제보다는 하리보 젤리나 유아용 비타민 느낌이 강함</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3114,17 +3140,17 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 사은품 품질 구성 — 동봉된 사은품의 품질이 저렴한 제품 같아 아쉬움</t>
+          <t>아쉬운 사은품 품질 — 사은품 구성이 시중 다이소 판매 제품으로 제공되어 아쉬움</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>호불호 갈리는 감기약 맛 — 오렌지약 또는 감기약 맛이 느껴져 맛에 대한 아쉬움이 있음</t>
+          <t>아쉬운 감기약 느낌 맛 — 오렌지 맛이 감기약 느낌과 유사하여 맛 면에서 아쉬움</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>매우 강한 신맛의 자극 — 분말 그대로 섭취 시 신맛이 지나치게 강해 물과 함께 복용해야 함</t>
+          <t>매우 강한 신맛 — 분말 제형 특성상 신맛이 강해 물 없이 섭취하기 어려움</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3162,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>34,000원</t>
+          <t>35,900원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -3354,12 +3380,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -3411,12 +3437,12 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>아일로</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
           <t>가농</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>아일로</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -3468,12 +3494,12 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>단백이 계란흰자 에그 프로틴 40개입(달걀 단백질 간편식)+(증정)단백이 구운맛 2개</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -3531,7 +3557,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>118</v>
@@ -3543,19 +3569,19 @@
         <v>1769</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>72</v>
       </c>
       <c r="I19" s="3" t="n">
+        <v>761</v>
+      </c>
+      <c r="J19" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="J19" s="3" t="n">
-        <v>761</v>
-      </c>
       <c r="K19" s="3" t="n">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>221</v>
@@ -3569,68 +3595,70 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>더부룩함 줄이는 소화 개선 — 속 답답함과 소화 불량을 빠르게 가라앉혀 편안함을 줌
-풍성하고 저렴한 사은품 — 추가 포수 및 단백질바 등 증정 구성품이 풍성하고 가성비가 높음
-고소하고 부담 없는 풍미 — 고소한 맛이 나서 질리지 않고 지속적으로 먹기 좋음</t>
+          <t>더부룩함 및 소화 개선 — 섭취 후 더부룩함이 개선되고 속이 편안해짐을 느낌
+풍성한 증정품 구성 — 추가 10포와 단백질바 등 다양한 사은품 구성이 풍성함
+고소하고 맛있는 맛 — 고소하고 맛있어 거부감 없이 매일 먹기 좋음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>개별 스틱 타입의 편리성 — 가방에 넣고 다니기 쉽고 복용 타이밍을 맞추기 용이함
-우수한 숙취 해소 성능 — 음주 전후 섭취 시 다음 날 숙취 없이 속이 편안함
-깔끔하고 가벼운 목넘김 — 텁텁함이 없고 깔끔한 고농축 제형이라 부담 없이 넘어감</t>
+          <t>뛰어난 숙취 해소 효과 — 음주 전후 섭취 시 다음날 속이 편안하고 회복이 빠름
+깔끔한 패키지 구성 — 세트 포장이 세련되고 구성이 넉넉하여 지인 선물용으로 적합함
+간편한 휴대와 목넘김 — 스틱 개별 포장이라 휴대하기 쉽고 맛이 텁텁하지 않음</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>촉촉하고 부드러운 육질 — 퍽퍽하지 않고 살이 촉촉하여 식감이 뛰어남
-다양하고 질리지 않는 맛 — 종류가 다채로워 질리지 않고 지속적으로 다이어트 식단을 이어감</t>
+          <t>촉촉하고 부드러운 식감 — 닭가슴살이 퍽퍽하지 않고 부드러워 맛있게 먹기 좋음
+질리지 않는 다양한 맛 — 36가지의 다채로운 맛으로 구성되어 매일 먹어도 질리지 않음</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>속이 편안한 소화 지원 — 과식이나 밀가루 음식 섭취 후 답답한 속을 신속하게 완화함
-미숫가루 같은 고소함 — 텁텁하지 않고 꼬수운 미숫가루 맛이 나서 먹기 수월함</t>
+          <t>속 더부룩함 및 소화 개선 — 밀가루나 외식 후 섭취 시 소화가 잘되고 속이 편안해짐
+고소한 미숫가루 맛 — 텁텁하지 않고 미숫가루처럼 고소한 맛이 나 먹기 좋음
+알찬 상품과 증정 구성 — 추가 증정포와 견과류바 등 구성이 풍성하여 만족스러움</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>취향 저격의 맛있는 효소 — 크림소다, 쿠키앤크림 등 기분 좋게 먹을 수 있는 풍미임
-푸짐하고 센스 있는 사은품 — 포토카드 및 단백질바 등 추가 구성품이 알차게 동봉됨</t>
+          <t>다양하고 맛있는 맛 — 쿠키앤크림, 크림소다 등 다양한 맛이 모두 맛있음
+매력적인 포토카드 증정 — 아이돌 포토카드와 단백질바 구성이 포함되어 만족스러움</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>전자레인지 조리의 간편함 — 데우기만 하면 바로 먹을 수 있어 식사 대용으로 편함
-다채롭고 촉촉한 식감 — 떡볶이 맛 등 맛이 다양하고 부드러워 식단 관리에 유용함</t>
+          <t>촉촉한 식감과 다채로운 맛 — 특색 있고 맛있는 양념과 촉촉한 식감이 만족스러움
+간편한 전자레인지 조리 — 전자레인지에 데우기만 하면 되어 간편하게 먹기 편함
+저렴한 가격과 빠른 배송 — 다양한 구성 대비 가격이 저렴하고 배송이 빠름</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>계란 흰자의 간편한 영양 — 노른자 없이 비리지 않은 흰자만으로 부담 없이 단백질을 챙김
-자극 없이 다양한 풍미 — 훈제, 짭짤한 맛 등 종류가 다양해 간식으로 즐기기 좋음</t>
+          <t>고급스럽고 예쁜 포장 — 패키지와 오간자 포장이 예뻐 선물용으로 훌륭함
+거부감 없는 맛과 편리함 — 앰플 제형으로 맛이 좋고 하루 한 병 간편하게 섭취함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>예쁘고 고급스러운 패키지 — 오간자 포장과 플리츠백 등 디자인이 인상적임
-기분 좋은 맛과 섭취 편의 — 맛이 좋고 하루 한 병씩 마시기 간편함</t>
+          <t>깔끔한 흰자 단백질 — 노른자가 없어 퍽퍽하지 않고 비리지 않게 단백질을 챙김
+껍질 까기 없는 간편함 — 껍질을 까는 번거로움 없이 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>다채로운 20종 패키지 — 종류가 많아 매일 질리지 않고 다이어트 식단을 즐길 수 있음
-촉촉한 식감과 조리 편의 — 부드러운 육질에 전자레인지 전용 용기가 포함되어 조리가 편리함</t>
+          <t>질리지 않는 다채로운 메뉴 — 닭가슴살 외 다양한 종류가 포함되어 질리지 않고 먹기 좋음
+렌지용 용기 제공의 편리함 — 증정받은 전용 용기 덕분에 전자레인지 조리가 편리함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 달콤함 — 느끼하거나 비리지 않고 일반 음료처럼 달콤하게 마실 수 있음
-포만감 있는 운동 후 보충 — 운동 후 단백질 보충에 용이하며 적절한 포만감을 유지해줌</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>비린 맛 없는 달콤함 — 단백질 특유의 비린 맛이나 느끼함 없이 달콤하게 마심
+든든한 포만감 형성 — 운동 후나 간식 대용으로 마시면 은근히 포만감이 생김</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -3639,15 +3667,20 @@
       <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>증정 기프티콘 안내 미흡 — 이벤트 기프티콘 수령 및 확인 방법에 대한 안내가 부족함</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>다소 깨끗하지 않은 박스 — 배송된 포장 박스 상태가 깨끗하지 않아 아쉬움</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>단일 맛 구성의 아쉬움 — 여러 맛을 섞어 구매할 수 있는 혼합 옵션이 없어 아쉬움
+박스 포장 상태 미흡 — 외포장 박스가 재활용된 듯 깨끗하지 않은 상태로 도착함</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -3689,12 +3722,12 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
+          <t>65,900원</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
           <t>39,000원</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>65,900원</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -3847,7 +3880,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3863,7 +3896,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3879,7 +3912,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3911,7 +3944,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
